--- a/system_development/Orichalcum/v0.2/Software_design/v2-cover-control/VIBROMETER SCAN SETTINGS.xlsx
+++ b/system_development/Orichalcum/v0.2/Software_design/v2-cover-control/VIBROMETER SCAN SETTINGS.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\In-situ-monitoring-of-powder-bed-fusion-additive-manufacturing\system_development\Orichalcum\v0.2\Software_design\v2-cover-control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D063A036-9C91-402B-AA8B-3268F6780DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747B8E91-D054-480F-BBF0-D9D2F290663B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4980" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scan Parameters" sheetId="2" r:id="rId1"/>
     <sheet name="Device Settings" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="143">
   <si>
     <t>Receiver</t>
   </si>
@@ -475,6 +476,12 @@
   </si>
   <si>
     <t>3D SS HTML &amp; 2D heatmap generated</t>
+  </si>
+  <si>
+    <t>AL Scan</t>
+  </si>
+  <si>
+    <t>"etched" AL sample</t>
   </si>
 </sst>
 </file>
@@ -998,7 +1005,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F5A5D31-C167-4FC4-94A5-027E9DD85F49}">
-  <dimension ref="B2:P19"/>
+  <dimension ref="B2:P20"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.21875" customWidth="1"/>
@@ -1649,6 +1656,35 @@
       </c>
       <c r="P19" t="s">
         <v>139</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="I20" s="6">
+        <v>3</v>
+      </c>
+      <c r="J20">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
